--- a/src/data/TAS.xlsx
+++ b/src/data/TAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matem\Documents\Proyecto Sintaxis Node\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DD18F9-235C-4D94-AF47-10538C0F1DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF9648C-370C-49BD-B0E1-BE728D220711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/data/TAS.xlsx
+++ b/src/data/TAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matem\Documents\Proyecto Sintaxis Node\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF9648C-370C-49BD-B0E1-BE728D220711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAB00A8-F5D4-488B-BD8D-0915573A0DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="118">
   <si>
     <t>Program</t>
   </si>
@@ -824,14 +824,23 @@
     <t xml:space="preserve">For </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">for ( </t>
+    <t>Condicion</t>
+  </si>
+  <si>
+    <t>TerminoLogico CondicionPrima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CondicionPrima </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>|</t>
     </r>
     <r>
       <rPr>
@@ -841,16 +850,27 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Asignacion </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">; </t>
+      <t xml:space="preserve"> TerminoLogico CondicionPrima</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TerminoLogico </t>
+  </si>
+  <si>
+    <t>FactorLogico TerminoLogicoPrima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TerminoLogicoPrima </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp; </t>
     </r>
     <r>
       <rPr>
@@ -860,17 +880,13 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Condicion </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">) { </t>
-    </r>
+      <t>FactorLogico TerminoLogicoPrima </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FactorLogico </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -879,6 +895,255 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">opRel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExpArit</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FactorLogico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">opRel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExpArit</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">opRel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExpArit</t>
+    </r>
+  </si>
+  <si>
+    <t>cteCadena</t>
+  </si>
+  <si>
+    <t>[ cteReal ]</t>
+  </si>
+  <si>
+    <t>Leer ;</t>
+  </si>
+  <si>
+    <t>{ Condicion }</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Program </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">id ; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DeclaracionVar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Secuencia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>cteReal</t>
+  </si>
+  <si>
+    <t>ExpArit</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, ExpArit ListaElementosPrim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Asignacion :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">{ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t xml:space="preserve">Secuencia </t>
     </r>
     <r>
@@ -892,275 +1157,7 @@
     </r>
   </si>
   <si>
-    <t>Condicion</t>
-  </si>
-  <si>
-    <t>TerminoLogico CondicionPrima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CondicionPrima </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> TerminoLogico CondicionPrima</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TerminoLogico </t>
-  </si>
-  <si>
-    <t>FactorLogico TerminoLogicoPrima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TerminoLogicoPrima </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FactorLogico TerminoLogicoPrima </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">FactorLogico </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">opRel </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExpArit</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FactorLogico</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">opRel </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExpArit</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">opRel </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExpArit</t>
-    </r>
-  </si>
-  <si>
-    <t>cteCadena</t>
-  </si>
-  <si>
-    <t>[ cteReal ]</t>
-  </si>
-  <si>
-    <t>Leer ;</t>
-  </si>
-  <si>
-    <t>{ Condicion }</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Program </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">id ; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>DeclaracionVar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Secuencia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>}</t>
-    </r>
-  </si>
-  <si>
-    <t>cteReal</t>
-  </si>
-  <si>
-    <t>ExpArit</t>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>, ExpArit ListaElementosPrim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>a</t>
-    </r>
+    <t>:</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1470,6 +1467,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1685,7 +1683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG998"/>
+  <dimension ref="A1:AH998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1721,7 +1719,7 @@
     <col min="33" max="33" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1805,7 +1803,7 @@
         <v>26</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>27</v>
@@ -1817,15 +1815,18 @@
         <v>29</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="AH1" s="39" t="s">
+        <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -1858,7 +1859,7 @@
       <c r="AE2" s="9"/>
       <c r="AF2" s="10"/>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>31</v>
       </c>
@@ -1898,7 +1899,7 @@
       <c r="AE3" s="15"/>
       <c r="AF3" s="14"/>
     </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
@@ -1936,7 +1937,7 @@
       <c r="AE4" s="15"/>
       <c r="AF4" s="14"/>
     </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>36</v>
       </c>
@@ -1974,7 +1975,7 @@
       <c r="AE5" s="15"/>
       <c r="AF5" s="14"/>
     </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>38</v>
       </c>
@@ -2010,11 +2011,11 @@
       <c r="AC6" s="15"/>
       <c r="AD6" s="14"/>
       <c r="AE6" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF6" s="14"/>
     </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>40</v>
       </c>
@@ -2062,7 +2063,7 @@
       <c r="AE7" s="15"/>
       <c r="AF7" s="14"/>
     </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>42</v>
       </c>
@@ -2076,7 +2077,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>44</v>
@@ -2110,7 +2111,7 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="14"/>
     </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>48</v>
       </c>
@@ -2150,7 +2151,7 @@
       <c r="AE9" s="15"/>
       <c r="AF9" s="14"/>
     </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>50</v>
       </c>
@@ -2188,7 +2189,7 @@
       <c r="AE10" s="15"/>
       <c r="AF10" s="14"/>
     </row>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>52</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>54</v>
       </c>
@@ -2293,17 +2294,19 @@
       <c r="Z12" s="12"/>
       <c r="AA12" s="14"/>
       <c r="AB12" s="14"/>
-      <c r="AC12" s="15"/>
+      <c r="AC12" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="AD12" s="14"/>
       <c r="AE12" s="23" t="s">
         <v>55</v>
       </c>
       <c r="AF12" s="14"/>
       <c r="AG12" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
@@ -2350,7 +2353,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" ht="13.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>58</v>
       </c>
@@ -2409,8 +2412,11 @@
       <c r="AF14" s="16" t="s">
         <v>39</v>
       </c>
+      <c r="AH14" s="14" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>61</v>
       </c>
@@ -2457,7 +2463,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>63</v>
       </c>
@@ -2468,7 +2474,9 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="G16" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
@@ -2518,8 +2526,11 @@
       <c r="AF16" s="16" t="s">
         <v>39</v>
       </c>
+      <c r="AH16" s="14" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>66</v>
       </c>
@@ -2566,7 +2577,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -2577,7 +2588,9 @@
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
@@ -2629,8 +2642,11 @@
       <c r="AF18" s="16" t="s">
         <v>39</v>
       </c>
+      <c r="AH18" s="14" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>70</v>
       </c>
@@ -2674,10 +2690,10 @@
       </c>
       <c r="AF19" s="14"/>
       <c r="AG19" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>74</v>
       </c>
@@ -2715,7 +2731,7 @@
       </c>
       <c r="AF20" s="14"/>
     </row>
-    <row r="21" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>76</v>
       </c>
@@ -2762,7 +2778,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>78</v>
       </c>
@@ -2791,7 +2807,7 @@
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
       <c r="Z22" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AA22" s="14"/>
       <c r="AB22" s="14"/>
@@ -2802,7 +2818,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>79</v>
       </c>
@@ -2840,7 +2856,7 @@
       <c r="AE23" s="15"/>
       <c r="AF23" s="14"/>
     </row>
-    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>81</v>
       </c>
@@ -2878,7 +2894,7 @@
       <c r="AE24" s="15"/>
       <c r="AF24" s="14"/>
     </row>
-    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>83</v>
       </c>
@@ -2924,7 +2940,7 @@
       </c>
       <c r="AF25" s="14"/>
     </row>
-    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>86</v>
       </c>
@@ -2964,7 +2980,7 @@
       <c r="AE26" s="15"/>
       <c r="AF26" s="14"/>
     </row>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>88</v>
       </c>
@@ -3002,7 +3018,7 @@
       <c r="AE27" s="15"/>
       <c r="AF27" s="14"/>
     </row>
-    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>90</v>
       </c>
@@ -3042,7 +3058,7 @@
       <c r="AE28" s="15"/>
       <c r="AF28" s="14"/>
     </row>
-    <row r="29" spans="1:33" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>92</v>
       </c>
@@ -3080,7 +3096,7 @@
       <c r="AE29" s="15"/>
       <c r="AF29" s="14"/>
     </row>
-    <row r="30" spans="1:33" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>94</v>
       </c>
@@ -3101,7 +3117,7 @@
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
       <c r="R30" s="16" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="S30" s="12"/>
       <c r="T30" s="12"/>
@@ -3118,13 +3134,13 @@
       <c r="AE30" s="15"/>
       <c r="AF30" s="14"/>
     </row>
-    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="13"/>
@@ -3135,7 +3151,7 @@
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
       <c r="L31" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
@@ -3144,11 +3160,11 @@
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
       <c r="S31" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T31" s="12"/>
       <c r="U31" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
@@ -3160,11 +3176,11 @@
       <c r="AC31" s="15"/>
       <c r="AD31" s="14"/>
       <c r="AE31" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF31" s="14"/>
     </row>
-    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>36</v>
       </c>
@@ -3202,7 +3218,7 @@
     </row>
     <row r="33" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -3239,7 +3255,7 @@
       <c r="Z33" s="12"/>
       <c r="AA33" s="14"/>
       <c r="AB33" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC33" s="15"/>
       <c r="AD33" s="14"/>
@@ -3248,11 +3264,11 @@
     </row>
     <row r="34" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="13"/>
@@ -3263,7 +3279,7 @@
       <c r="J34" s="12"/>
       <c r="K34" s="12"/>
       <c r="L34" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
@@ -3272,7 +3288,7 @@
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
       <c r="S34" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T34" s="12"/>
       <c r="U34" s="12"/>
@@ -3281,20 +3297,20 @@
       <c r="X34" s="12"/>
       <c r="Y34" s="12"/>
       <c r="Z34" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA34" s="14"/>
       <c r="AB34" s="14"/>
       <c r="AC34" s="15"/>
       <c r="AD34" s="14"/>
       <c r="AE34" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AF34" s="14"/>
     </row>
     <row r="35" spans="1:32" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -3330,7 +3346,7 @@
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
       <c r="AA35" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AB35" s="16" t="s">
         <v>39</v>
@@ -3342,17 +3358,17 @@
     </row>
     <row r="36" spans="1:32" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D36" s="28"/>
       <c r="E36" s="29"/>
       <c r="F36" s="28"/>
       <c r="G36" s="34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H36" s="28"/>
       <c r="I36" s="28"/>
@@ -3366,11 +3382,11 @@
       <c r="Q36" s="28"/>
       <c r="R36" s="28"/>
       <c r="S36" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T36" s="28"/>
       <c r="U36" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="V36" s="28"/>
       <c r="W36" s="28"/>
@@ -3382,7 +3398,7 @@
       <c r="AC36" s="32"/>
       <c r="AD36" s="31"/>
       <c r="AE36" s="33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AF36" s="31"/>
     </row>
@@ -4352,6 +4368,6 @@
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/data/TAS.xlsx
+++ b/src/data/TAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matem\Documents\Proyecto Sintaxis Node\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAB00A8-F5D4-488B-BD8D-0915573A0DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FCD159-7615-48E0-B885-FF2F19CC994A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="119">
   <si>
     <t>Program</t>
   </si>
@@ -629,14 +629,17 @@
     <t>ExpArit ListaCadena</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cadena </t>
+    <t>ListaCadena</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -646,518 +649,512 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t>ListaEscritura</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SiEntSino </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Condicion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> then { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Secuencia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>SiEntSino'</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SiEntSino' </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">else { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Secuencia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">While </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">while </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Condicion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">do { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Secuencia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">For </t>
+  </si>
+  <si>
+    <t>Condicion</t>
+  </si>
+  <si>
+    <t>TerminoLogico CondicionPrima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CondicionPrima </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> TerminoLogico CondicionPrima</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TerminoLogico </t>
+  </si>
+  <si>
+    <t>FactorLogico TerminoLogicoPrima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TerminoLogicoPrima </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FactorLogico TerminoLogicoPrima </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FactorLogico </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">opRel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExpArit</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FactorLogico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">opRel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExpArit</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">opRel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ExpArit</t>
+    </r>
+  </si>
+  <si>
+    <t>cteCadena</t>
+  </si>
+  <si>
+    <t>[ cteReal ]</t>
+  </si>
+  <si>
+    <t>Leer ;</t>
+  </si>
+  <si>
+    <t>{ Condicion }</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Program </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">id ; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DeclaracionVar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Secuencia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>cteReal</t>
+  </si>
+  <si>
+    <t>ExpArit</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, ExpArit ListaElementosPrim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Asignacion :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ExpArit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">{ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Secuencia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+  </si>
+  <si>
+    <t>:</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cteCadena </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t xml:space="preserve">ListaCadena </t>
     </r>
-  </si>
-  <si>
-    <t>ListaCadena</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ListaEscritura</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SiEntSino </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Condicion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> then { </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Secuencia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>SiEntSino'</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SiEntSino' </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">else { </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Secuencia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>}</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">While </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">while </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Condicion </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">do { </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Secuencia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>}</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">For </t>
-  </si>
-  <si>
-    <t>Condicion</t>
-  </si>
-  <si>
-    <t>TerminoLogico CondicionPrima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CondicionPrima </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> TerminoLogico CondicionPrima</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TerminoLogico </t>
-  </si>
-  <si>
-    <t>FactorLogico TerminoLogicoPrima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TerminoLogicoPrima </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FactorLogico TerminoLogicoPrima </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">FactorLogico </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">opRel </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExpArit</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FactorLogico</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">opRel </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExpArit</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">opRel </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ExpArit</t>
-    </r>
-  </si>
-  <si>
-    <t>cteCadena</t>
-  </si>
-  <si>
-    <t>[ cteReal ]</t>
-  </si>
-  <si>
-    <t>Leer ;</t>
-  </si>
-  <si>
-    <t>{ Condicion }</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Program </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">id ; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>DeclaracionVar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Secuencia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>}</t>
-    </r>
-  </si>
-  <si>
-    <t>cteReal</t>
-  </si>
-  <si>
-    <t>ExpArit</t>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>, ExpArit ListaElementosPrim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Asignacion :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">ExpArit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">{ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Secuencia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-  </si>
-  <si>
-    <t>:</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1464,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1683,43 +1680,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH998"/>
+  <dimension ref="A1:AI998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" customWidth="1"/>
     <col min="2" max="2" width="45.109375" customWidth="1"/>
     <col min="3" max="3" width="47.109375" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="40.21875" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" customWidth="1"/>
-    <col min="9" max="9" width="20.21875" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="47.88671875" customWidth="1"/>
-    <col min="12" max="12" width="42.44140625" customWidth="1"/>
-    <col min="13" max="14" width="10.6640625" customWidth="1"/>
-    <col min="15" max="15" width="22.33203125" customWidth="1"/>
-    <col min="16" max="16" width="53.21875" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" customWidth="1"/>
-    <col min="18" max="18" width="64.88671875" customWidth="1"/>
-    <col min="19" max="19" width="42" customWidth="1"/>
-    <col min="20" max="20" width="25.77734375" customWidth="1"/>
-    <col min="21" max="21" width="42.44140625" customWidth="1"/>
-    <col min="22" max="22" width="23.21875" customWidth="1"/>
-    <col min="23" max="24" width="22" customWidth="1"/>
-    <col min="25" max="25" width="10.6640625" customWidth="1"/>
-    <col min="26" max="26" width="43.77734375" customWidth="1"/>
-    <col min="27" max="27" width="50.21875" customWidth="1"/>
-    <col min="28" max="28" width="39.88671875" customWidth="1"/>
-    <col min="29" max="29" width="25.44140625" customWidth="1"/>
-    <col min="30" max="30" width="10.6640625" customWidth="1"/>
-    <col min="31" max="31" width="43.6640625" customWidth="1"/>
-    <col min="32" max="32" width="10.6640625" customWidth="1"/>
-    <col min="33" max="33" width="16.5546875" customWidth="1"/>
+    <col min="4" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="40.21875" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="25.77734375" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="47.88671875" customWidth="1"/>
+    <col min="13" max="13" width="42.44140625" customWidth="1"/>
+    <col min="14" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" customWidth="1"/>
+    <col min="17" max="17" width="53.21875" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
+    <col min="19" max="19" width="64.88671875" customWidth="1"/>
+    <col min="20" max="20" width="42" customWidth="1"/>
+    <col min="21" max="21" width="25.77734375" customWidth="1"/>
+    <col min="22" max="22" width="42.44140625" customWidth="1"/>
+    <col min="23" max="23" width="23.21875" customWidth="1"/>
+    <col min="24" max="25" width="22" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="43.77734375" customWidth="1"/>
+    <col min="28" max="28" width="50.21875" customWidth="1"/>
+    <col min="29" max="29" width="39.88671875" customWidth="1"/>
+    <col min="30" max="30" width="25.44140625" customWidth="1"/>
+    <col min="31" max="31" width="10.6640625" customWidth="1"/>
+    <col min="32" max="32" width="43.6640625" customWidth="1"/>
+    <col min="33" max="33" width="10.6640625" customWidth="1"/>
+    <col min="34" max="34" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1731,102 +1728,105 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH1" s="39" t="s">
-        <v>117</v>
+      <c r="AH1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -1850,16 +1850,17 @@
       <c r="V2" s="7"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="8"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="10"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="10"/>
     </row>
-    <row r="3" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>31</v>
       </c>
@@ -1870,10 +1871,10 @@
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12"/>
+      <c r="H3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
@@ -1892,14 +1893,15 @@
       <c r="X3" s="12"/>
       <c r="Y3" s="12"/>
       <c r="Z3" s="12"/>
-      <c r="AA3" s="14"/>
+      <c r="AA3" s="12"/>
       <c r="AB3" s="14"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="14"/>
     </row>
-    <row r="4" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
@@ -1930,24 +1932,25 @@
       <c r="X4" s="12"/>
       <c r="Y4" s="12"/>
       <c r="Z4" s="12"/>
-      <c r="AA4" s="14"/>
+      <c r="AA4" s="12"/>
       <c r="AB4" s="14"/>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="15"/>
-      <c r="AF4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="14"/>
     </row>
-    <row r="5" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="16"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -1968,14 +1971,15 @@
       <c r="X5" s="12"/>
       <c r="Y5" s="12"/>
       <c r="Z5" s="12"/>
-      <c r="AA5" s="14"/>
+      <c r="AA5" s="12"/>
       <c r="AB5" s="14"/>
-      <c r="AC5" s="15"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="15"/>
-      <c r="AF5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="14"/>
     </row>
-    <row r="6" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>38</v>
       </c>
@@ -1984,7 +1988,7 @@
       <c r="D6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -2006,16 +2010,17 @@
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
-      <c r="AA6" s="14"/>
+      <c r="AA6" s="12"/>
       <c r="AB6" s="14"/>
-      <c r="AC6" s="15"/>
-      <c r="AD6" s="14"/>
-      <c r="AE6" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG6" s="14"/>
     </row>
-    <row r="7" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>40</v>
       </c>
@@ -2027,28 +2032,28 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13" t="s">
-        <v>41</v>
-      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="12"/>
       <c r="K7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="L7" s="13" t="s">
+        <v>41</v>
+      </c>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
-      <c r="P7" s="13" t="s">
+      <c r="P7" s="12"/>
+      <c r="Q7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="13" t="s">
+      <c r="R7" s="12"/>
+      <c r="S7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="S7" s="12"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
@@ -2056,14 +2061,15 @@
       <c r="X7" s="12"/>
       <c r="Y7" s="12"/>
       <c r="Z7" s="12"/>
-      <c r="AA7" s="14"/>
+      <c r="AA7" s="12"/>
       <c r="AB7" s="14"/>
-      <c r="AC7" s="15"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="15"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="14"/>
     </row>
-    <row r="8" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>42</v>
       </c>
@@ -2076,27 +2082,27 @@
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
-      <c r="I8" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J8" s="13" t="s">
+      <c r="I8" s="12"/>
+      <c r="J8" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="L8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
-      <c r="P8" s="13" t="s">
+      <c r="P8" s="12"/>
+      <c r="Q8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="16" t="s">
+      <c r="R8" s="12"/>
+      <c r="S8" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="S8" s="12"/>
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
@@ -2104,14 +2110,15 @@
       <c r="X8" s="12"/>
       <c r="Y8" s="12"/>
       <c r="Z8" s="12"/>
-      <c r="AA8" s="14"/>
+      <c r="AA8" s="12"/>
       <c r="AB8" s="14"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="15"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="14"/>
     </row>
-    <row r="9" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>48</v>
       </c>
@@ -2123,10 +2130,10 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-      <c r="H9" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
@@ -2144,14 +2151,15 @@
       <c r="X9" s="12"/>
       <c r="Y9" s="12"/>
       <c r="Z9" s="12"/>
-      <c r="AA9" s="14"/>
+      <c r="AA9" s="12"/>
       <c r="AB9" s="14"/>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="14"/>
     </row>
-    <row r="10" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>50</v>
       </c>
@@ -2182,14 +2190,15 @@
       <c r="X10" s="12"/>
       <c r="Y10" s="12"/>
       <c r="Z10" s="12"/>
-      <c r="AA10" s="14"/>
+      <c r="AA10" s="12"/>
       <c r="AB10" s="14"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="14"/>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="14"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="14"/>
     </row>
-    <row r="11" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>52</v>
       </c>
@@ -2198,32 +2207,32 @@
       <c r="D11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="21" t="s">
-        <v>39</v>
-      </c>
+      <c r="M11" s="12"/>
       <c r="N11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="12"/>
+      <c r="O11" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="P11" s="12"/>
-      <c r="Q11" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" s="12"/>
+      <c r="T11" s="21"/>
       <c r="U11" s="21" t="s">
         <v>39</v>
       </c>
@@ -2236,28 +2245,31 @@
       <c r="X11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="21" t="s">
-        <v>39</v>
-      </c>
+      <c r="Y11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z11" s="12"/>
       <c r="AA11" s="21" t="s">
         <v>39</v>
       </c>
       <c r="AB11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE11" s="22" t="s">
+      <c r="AC11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD11" s="15"/>
+      <c r="AE11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF11" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="AF11" s="16" t="s">
+      <c r="AG11" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>54</v>
       </c>
@@ -2266,17 +2278,17 @@
         <v>55</v>
       </c>
       <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="12"/>
+      <c r="M12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -2284,29 +2296,30 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="13" t="s">
+      <c r="U12" s="12"/>
+      <c r="V12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="14"/>
+      <c r="AA12" s="12"/>
       <c r="AB12" s="14"/>
-      <c r="AC12" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="23" t="s">
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="AF12" s="14"/>
-      <c r="AG12" s="37" t="s">
-        <v>114</v>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="37" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
@@ -2315,17 +2328,17 @@
         <v>56</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="36"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="12"/>
+      <c r="M13" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="12"/>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
@@ -2333,27 +2346,28 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="13" t="s">
+      <c r="U13" s="12"/>
+      <c r="V13" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="14"/>
+      <c r="AA13" s="12"/>
       <c r="AB13" s="14"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="23" t="s">
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="15"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="37" t="s">
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="37" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="13.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" ht="13.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>58</v>
       </c>
@@ -2362,61 +2376,68 @@
       <c r="D14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="12"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="L14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" s="19"/>
       <c r="N14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="12"/>
+      <c r="O14" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="P14" s="12"/>
       <c r="Q14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="R14" s="12"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="19" t="s">
+      <c r="R14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T14" s="16"/>
+      <c r="U14" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="U14" s="18" t="s">
+      <c r="V14" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
-      <c r="Z14" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="Z14" s="12"/>
       <c r="AA14" s="16" t="s">
         <v>39</v>
       </c>
       <c r="AB14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE14" s="15"/>
-      <c r="AF14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH14" s="14" t="s">
+      <c r="AC14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD14" s="15"/>
+      <c r="AE14" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF14" s="15"/>
+      <c r="AG14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI14" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>61</v>
       </c>
@@ -2425,17 +2446,17 @@
         <v>62</v>
       </c>
       <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="12"/>
+      <c r="M15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
@@ -2443,27 +2464,28 @@
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
       <c r="T15" s="12"/>
-      <c r="U15" s="13" t="s">
+      <c r="U15" s="12"/>
+      <c r="V15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="V15" s="12"/>
       <c r="W15" s="12"/>
       <c r="X15" s="12"/>
       <c r="Y15" s="12"/>
       <c r="Z15" s="12"/>
-      <c r="AA15" s="14"/>
+      <c r="AA15" s="12"/>
       <c r="AB15" s="14"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="23" t="s">
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="14"/>
+      <c r="AF15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="AF15" s="14"/>
-      <c r="AG15" s="37" t="s">
+      <c r="AG15" s="14"/>
+      <c r="AH15" s="37" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" ht="13.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>63</v>
       </c>
@@ -2472,65 +2494,72 @@
       <c r="D16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="L16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="12"/>
       <c r="N16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="12"/>
+      <c r="O16" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="P16" s="12"/>
       <c r="Q16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="R16" s="12"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="R16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T16" s="16"/>
       <c r="U16" s="16" t="s">
         <v>39</v>
       </c>
       <c r="V16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="W16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="W16" s="16" t="s">
+      <c r="X16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="X16" s="12"/>
       <c r="Y16" s="12"/>
-      <c r="Z16" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="Z16" s="12"/>
       <c r="AA16" s="16" t="s">
         <v>39</v>
       </c>
       <c r="AB16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH16" s="14" t="s">
+      <c r="AC16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD16" s="15"/>
+      <c r="AE16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF16" s="15"/>
+      <c r="AG16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI16" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>66</v>
       </c>
@@ -2539,45 +2568,46 @@
         <v>67</v>
       </c>
       <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="12"/>
+      <c r="M17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="M17" s="16"/>
-      <c r="N17" s="12"/>
+      <c r="N17" s="16"/>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
-      <c r="S17" s="16"/>
+      <c r="S17" s="12"/>
       <c r="T17" s="16"/>
-      <c r="U17" s="13" t="s">
+      <c r="U17" s="16"/>
+      <c r="V17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="V17" s="16"/>
       <c r="W17" s="16"/>
       <c r="X17" s="16"/>
-      <c r="Y17" s="12"/>
+      <c r="Y17" s="16"/>
       <c r="Z17" s="12"/>
-      <c r="AA17" s="14"/>
+      <c r="AA17" s="12"/>
       <c r="AB17" s="14"/>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="25" t="s">
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="37" t="s">
+      <c r="AG17" s="14"/>
+      <c r="AH17" s="37" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" ht="13.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
@@ -2586,32 +2616,36 @@
       <c r="D18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="12"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="L18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="12"/>
       <c r="N18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="O18" s="12"/>
+      <c r="O18" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="P18" s="12"/>
       <c r="Q18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="R18" s="12"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="R18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T18" s="16"/>
       <c r="U18" s="16" t="s">
         <v>39</v>
       </c>
@@ -2622,31 +2656,34 @@
         <v>39</v>
       </c>
       <c r="X18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y18" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="Z18" s="12"/>
       <c r="AA18" s="16" t="s">
         <v>39</v>
       </c>
       <c r="AB18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH18" s="14" t="s">
+      <c r="AC18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD18" s="15"/>
+      <c r="AE18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF18" s="15"/>
+      <c r="AG18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI18" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>70</v>
       </c>
@@ -2662,10 +2699,10 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
-      <c r="L19" s="16" t="s">
+      <c r="L19" s="12"/>
+      <c r="M19" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
       <c r="P19" s="12"/>
@@ -2673,27 +2710,28 @@
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
       <c r="T19" s="12"/>
-      <c r="U19" s="12" t="s">
+      <c r="U19" s="12"/>
+      <c r="V19" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="V19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
       <c r="Y19" s="12"/>
       <c r="Z19" s="12"/>
-      <c r="AA19" s="14"/>
+      <c r="AA19" s="12"/>
       <c r="AB19" s="14"/>
-      <c r="AC19" s="15"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="26" t="s">
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="15"/>
+      <c r="AE19" s="14"/>
+      <c r="AF19" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="AF19" s="14"/>
-      <c r="AG19" s="37" t="s">
-        <v>113</v>
+      <c r="AG19" s="14"/>
+      <c r="AH19" s="37" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>74</v>
       </c>
@@ -2707,8 +2745,8 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="16"/>
       <c r="N20" s="12"/>
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
@@ -2722,16 +2760,17 @@
       <c r="X20" s="12"/>
       <c r="Y20" s="12"/>
       <c r="Z20" s="12"/>
-      <c r="AA20" s="14"/>
+      <c r="AA20" s="12"/>
       <c r="AB20" s="14"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="17" t="s">
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="15"/>
+      <c r="AE20" s="14"/>
+      <c r="AF20" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="AF20" s="14"/>
+      <c r="AG20" s="14"/>
     </row>
-    <row r="21" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>76</v>
       </c>
@@ -2740,17 +2779,17 @@
         <v>77</v>
       </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
-      <c r="L21" s="27" t="s">
+      <c r="L21" s="12"/>
+      <c r="M21" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M21" s="12"/>
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
       <c r="P21" s="12"/>
@@ -2758,42 +2797,43 @@
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
       <c r="T21" s="12"/>
-      <c r="U21" s="27" t="s">
+      <c r="U21" s="12"/>
+      <c r="V21" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="V21" s="12"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
       <c r="Y21" s="12"/>
       <c r="Z21" s="12"/>
-      <c r="AA21" s="14"/>
+      <c r="AA21" s="12"/>
       <c r="AB21" s="14"/>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="23" t="s">
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="15"/>
+      <c r="AE21" s="14"/>
+      <c r="AF21" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="38" t="s">
+      <c r="AG21" s="14"/>
+      <c r="AH21" s="38" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>78</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="13"/>
       <c r="D22" s="12"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="12"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="27"/>
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
@@ -2801,24 +2841,25 @@
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
       <c r="T22" s="12"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="27"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
       <c r="Y22" s="12"/>
-      <c r="Z22" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA22" s="14"/>
+      <c r="Z22" s="12"/>
+      <c r="AA22" s="21" t="s">
+        <v>114</v>
+      </c>
       <c r="AB22" s="14"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="16" t="s">
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="15"/>
+      <c r="AE22" s="14"/>
+      <c r="AF22" s="23"/>
+      <c r="AG22" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>79</v>
       </c>
@@ -2829,10 +2870,10 @@
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="12"/>
+      <c r="J23" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="J23" s="12"/>
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -2849,14 +2890,15 @@
       <c r="X23" s="12"/>
       <c r="Y23" s="12"/>
       <c r="Z23" s="12"/>
-      <c r="AA23" s="14"/>
+      <c r="AA23" s="12"/>
       <c r="AB23" s="14"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="14"/>
+      <c r="AF23" s="15"/>
+      <c r="AG23" s="14"/>
     </row>
-    <row r="24" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>81</v>
       </c>
@@ -2868,10 +2910,10 @@
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
-      <c r="J24" s="16" t="s">
+      <c r="J24" s="12"/>
+      <c r="K24" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="K24" s="12"/>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
@@ -2887,14 +2929,15 @@
       <c r="X24" s="12"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="12"/>
-      <c r="AA24" s="14"/>
+      <c r="AA24" s="12"/>
       <c r="AB24" s="14"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="15"/>
-      <c r="AF24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="14"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="14"/>
     </row>
-    <row r="25" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>83</v>
       </c>
@@ -2903,17 +2946,17 @@
         <v>84</v>
       </c>
       <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="13" t="s">
+      <c r="J25" s="12"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
@@ -2921,28 +2964,29 @@
       <c r="R25" s="12"/>
       <c r="S25" s="12"/>
       <c r="T25" s="12"/>
-      <c r="U25" s="13" t="s">
+      <c r="U25" s="12"/>
+      <c r="V25" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="V25" s="12"/>
       <c r="W25" s="12"/>
       <c r="X25" s="12"/>
       <c r="Y25" s="12"/>
       <c r="Z25" s="12"/>
-      <c r="AA25" s="14"/>
+      <c r="AA25" s="12"/>
       <c r="AB25" s="14"/>
-      <c r="AC25" s="17" t="s">
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE25" s="14"/>
+      <c r="AF25" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG25" s="14"/>
+    </row>
+    <row r="26" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF25" s="14"/>
-    </row>
-    <row r="26" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2952,13 +2996,13 @@
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="16"/>
       <c r="L26" s="12"/>
-      <c r="M26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
@@ -2970,19 +3014,20 @@
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
       <c r="Y26" s="12"/>
-      <c r="Z26" s="16" t="s">
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="15"/>
+      <c r="AG26" s="14"/>
+    </row>
+    <row r="27" spans="1:35" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="14"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="14"/>
-    </row>
-    <row r="27" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>88</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2993,10 +3038,10 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="L27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
@@ -3011,39 +3056,42 @@
       <c r="X27" s="12"/>
       <c r="Y27" s="12"/>
       <c r="Z27" s="12"/>
-      <c r="AA27" s="14"/>
+      <c r="AA27" s="12"/>
       <c r="AB27" s="14"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="14"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="14"/>
     </row>
-    <row r="28" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="12"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
-      <c r="L28" s="12"/>
+      <c r="L28" s="16"/>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
-      <c r="O28" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="16"/>
       <c r="T28" s="12"/>
       <c r="U28" s="12"/>
       <c r="V28" s="12"/>
@@ -3051,16 +3099,17 @@
       <c r="X28" s="12"/>
       <c r="Y28" s="12"/>
       <c r="Z28" s="12"/>
-      <c r="AA28" s="14"/>
+      <c r="AA28" s="12"/>
       <c r="AB28" s="14"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="14"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="15"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="15"/>
+      <c r="AG28" s="14"/>
     </row>
-    <row r="29" spans="1:34" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -3076,10 +3125,10 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
-      <c r="P29" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="16" t="s">
+        <v>92</v>
+      </c>
       <c r="R29" s="12"/>
       <c r="S29" s="12"/>
       <c r="T29" s="12"/>
@@ -3089,16 +3138,17 @@
       <c r="X29" s="12"/>
       <c r="Y29" s="12"/>
       <c r="Z29" s="12"/>
-      <c r="AA29" s="14"/>
+      <c r="AA29" s="12"/>
       <c r="AB29" s="14"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="14"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="15"/>
+      <c r="AE29" s="14"/>
+      <c r="AF29" s="15"/>
+      <c r="AG29" s="14"/>
     </row>
-    <row r="30" spans="1:34" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -3116,10 +3166,10 @@
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
-      <c r="R30" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="S30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="T30" s="12"/>
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
@@ -3127,60 +3177,62 @@
       <c r="X30" s="12"/>
       <c r="Y30" s="12"/>
       <c r="Z30" s="12"/>
-      <c r="AA30" s="14"/>
+      <c r="AA30" s="12"/>
       <c r="AB30" s="14"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="14"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="15"/>
+      <c r="AE30" s="14"/>
+      <c r="AF30" s="15"/>
+      <c r="AG30" s="14"/>
     </row>
-    <row r="31" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" s="12"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
-      <c r="L31" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="M31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
-      <c r="S31" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="T31" s="12"/>
-      <c r="U31" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="V31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="U31" s="12"/>
+      <c r="V31" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
       <c r="Y31" s="12"/>
       <c r="Z31" s="12"/>
-      <c r="AA31" s="14"/>
+      <c r="AA31" s="12"/>
       <c r="AB31" s="14"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="14"/>
-      <c r="AE31" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="15"/>
+      <c r="AE31" s="14"/>
+      <c r="AF31" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG31" s="14"/>
     </row>
-    <row r="32" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>36</v>
       </c>
@@ -3209,23 +3261,24 @@
       <c r="X32" s="12"/>
       <c r="Y32" s="12"/>
       <c r="Z32" s="12"/>
-      <c r="AA32" s="14"/>
+      <c r="AA32" s="12"/>
       <c r="AB32" s="14"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="14"/>
-      <c r="AE32" s="15"/>
-      <c r="AF32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="15"/>
+      <c r="AE32" s="14"/>
+      <c r="AF32" s="15"/>
+      <c r="AG32" s="14"/>
     </row>
-    <row r="33" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="12"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
@@ -3233,18 +3286,18 @@
       <c r="J33" s="12"/>
       <c r="K33" s="12"/>
       <c r="L33" s="12"/>
-      <c r="M33" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="M33" s="12"/>
       <c r="N33" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="O33" s="12"/>
+      <c r="O33" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="P33" s="12"/>
-      <c r="Q33" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="R33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="S33" s="12"/>
       <c r="T33" s="12"/>
       <c r="U33" s="12"/>
@@ -3253,71 +3306,73 @@
       <c r="X33" s="12"/>
       <c r="Y33" s="12"/>
       <c r="Z33" s="12"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="16" t="s">
+      <c r="AA33" s="12"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD33" s="15"/>
+      <c r="AE33" s="14"/>
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="14"/>
+    </row>
+    <row r="34" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="14"/>
-      <c r="AE33" s="15"/>
-      <c r="AF33" s="14"/>
-    </row>
-    <row r="34" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="13"/>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
       <c r="K34" s="12"/>
-      <c r="L34" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="M34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="N34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
       <c r="R34" s="12"/>
-      <c r="S34" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="T34" s="12"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
       <c r="W34" s="12"/>
       <c r="X34" s="12"/>
       <c r="Y34" s="12"/>
-      <c r="Z34" s="13" t="s">
+      <c r="Z34" s="12"/>
+      <c r="AA34" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="15"/>
+      <c r="AE34" s="14"/>
+      <c r="AF34" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG34" s="14"/>
+    </row>
+    <row r="35" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="15"/>
-      <c r="AD34" s="14"/>
-      <c r="AE34" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF34" s="14"/>
-    </row>
-    <row r="35" spans="1:32" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>101</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="12"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
@@ -3325,18 +3380,18 @@
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
-      <c r="M35" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="M35" s="12"/>
       <c r="N35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="O35" s="12"/>
+      <c r="O35" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="P35" s="12"/>
-      <c r="Q35" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="R35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="S35" s="12"/>
       <c r="T35" s="12"/>
       <c r="U35" s="12"/>
@@ -3345,77 +3400,79 @@
       <c r="X35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
-      <c r="AA35" s="19" t="s">
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC35" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD35" s="15"/>
+      <c r="AE35" s="14"/>
+      <c r="AF35" s="15"/>
+      <c r="AG35" s="14"/>
+    </row>
+    <row r="36" spans="1:33" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
         <v>102</v>
-      </c>
-      <c r="AB35" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC35" s="15"/>
-      <c r="AD35" s="14"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="14"/>
-    </row>
-    <row r="36" spans="1:32" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="11" t="s">
-        <v>103</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" s="28"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="H36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="34" t="s">
+        <v>110</v>
+      </c>
       <c r="I36" s="28"/>
       <c r="J36" s="28"/>
       <c r="K36" s="28"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="30"/>
       <c r="N36" s="28"/>
       <c r="O36" s="28"/>
       <c r="P36" s="28"/>
       <c r="Q36" s="28"/>
       <c r="R36" s="28"/>
-      <c r="S36" s="30" t="s">
+      <c r="S36" s="28"/>
+      <c r="T36" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="U36" s="28"/>
+      <c r="V36" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="T36" s="28"/>
-      <c r="U36" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="V36" s="28"/>
       <c r="W36" s="28"/>
       <c r="X36" s="28"/>
       <c r="Y36" s="28"/>
       <c r="Z36" s="28"/>
-      <c r="AA36" s="31"/>
+      <c r="AA36" s="28"/>
       <c r="AB36" s="31"/>
-      <c r="AC36" s="32"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="AF36" s="31"/>
+      <c r="AC36" s="31"/>
+      <c r="AD36" s="32"/>
+      <c r="AE36" s="31"/>
+      <c r="AF36" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG36" s="31"/>
     </row>
-    <row r="37" spans="1:32" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G39" s="35"/>
+    <row r="37" spans="1:33" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="35"/>
     </row>
-    <row r="40" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
